--- a/evaluation_forms/047_technician_evaluation_form_westmin_area_22--evaluation_forms.xlsx
+++ b/evaluation_forms/047_technician_evaluation_form_westmin_area_22--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>What were your overall impressions of our technician's performance?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,133 +543,133 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ratings</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>performance ratings</t>
+          <t>Please rate the technician's communication skills -</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Please rate the technician's technical skills -</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>technician_name</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>technician name</t>
+          <t>Please rate the technician's problem-solving skills -</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>technician_id</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>technician id</t>
+          <t>What was the technician's attitude towards you?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Please rate the technician's overall service -</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>What was the most impressive aspect of the service?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rating 1</t>
+          <t>Was the service completed on time?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rating 2</t>
+          <t>Was the service completed within budget?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rating 3</t>
+          <t>Please rate the technician's professionalism -</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>score_1</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>score 1</t>
+          <t>Please rate the technician's timeliness -</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,248 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>score_2</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>score 2</t>
+          <t>Please submit this form once complete</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>score_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>score 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>evaluation_area</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>evaluation area</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>submitted by</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>submitted_on</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>submitted on</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>submitted at</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>technician_id</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>technician id</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>technician_name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>technician name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1029,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1057,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ratings_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1074,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ratings_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1091,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ratings_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1108,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ratings_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1125,102 +895,323 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>evaluation_area_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>westmin_1</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westmin 1</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>evaluation_area_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>westmin_2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westmin 2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>poor</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>on_time</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>On time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Late</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>early</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Early</t>
         </is>
       </c>
     </row>
